--- a/BKQBF_TAB-7.xlsx
+++ b/BKQBF_TAB-7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0ddff5975960f05/Dcts_BK_compartilhado/BI_Arquivos_compartilhado/c_Sistema_BKQBF/BK_Compra_Perfeita/CPerfect_Files_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="21" documentId="8_{E721577D-3948-4D5C-80B6-A4597D22FC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BBC267D-096B-4048-96DB-20AC44935206}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABELA CDD" sheetId="2" r:id="rId1"/>
@@ -50467,6 +50467,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003038969B0484BC4CA3D2193B8D466837" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="8ab212246e0cd10e6d6fb536f05e49d7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xmlns:ns3="3a1b5eaf-929c-4573-820b-891dab44de53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="57fa6bbb6a9bbb3abd7365671c522804" ns2:_="" ns3:_="">
     <xsd:import namespace="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
@@ -50695,27 +50715,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33820F0B-1B1E-4D3B-B941-4E6726A66AF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
+    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a1b5eaf-929c-4573-820b-891dab44de53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec0ddbf7-d703-48b2-bd3e-f07de892778d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97D70FD6-175A-4C5E-A4DF-C2412A55590C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A19E606C-7509-48F6-8181-D83FFC7AF7F5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50732,23 +50751,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97D70FD6-175A-4C5E-A4DF-C2412A55590C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33820F0B-1B1E-4D3B-B941-4E6726A66AF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3a1b5eaf-929c-4573-820b-891dab44de53"/>
-    <ds:schemaRef ds:uri="ec0ddbf7-d703-48b2-bd3e-f07de892778d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>